--- a/Team-Data/2008-09/12-21-2008-09.xlsx
+++ b/Team-Data/2008-09/12-21-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.63</v>
+        <v>0.615</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="J2" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L2" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P2" t="n">
         <v>23.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R2" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S2" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
         <v>21.1</v>
@@ -721,34 +788,34 @@
         <v>6.9</v>
       </c>
       <c r="X2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.3</v>
+        <v>96.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF2" t="n">
         <v>7</v>
       </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8</v>
-      </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>26</v>
@@ -769,40 +836,40 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>26</v>
       </c>
       <c r="AP2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR2" t="n">
         <v>18</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17</v>
-      </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -811,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -858,70 +925,70 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.1</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
         <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.488</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="P3" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.7</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="V3" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.5</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -951,40 +1018,40 @@
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -993,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1124,13 +1191,13 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
       </c>
       <c r="AM4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN4" t="n">
         <v>16</v>
@@ -1139,13 +1206,13 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>30</v>
@@ -1163,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1207,106 +1274,106 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.462</v>
+        <v>0.481</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>85.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L5" t="n">
         <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>18.7</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.802</v>
+        <v>0.799</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W5" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="AD5" t="n">
         <v>6</v>
       </c>
-      <c r="Z5" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>18</v>
-      </c>
       <c r="AE5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1318,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>6</v>
@@ -1333,10 +1400,10 @@
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
@@ -1348,19 +1415,19 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1392,61 +1459,61 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.885</v>
+        <v>0.846</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.6</v>
+        <v>38.1</v>
       </c>
       <c r="J6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.483</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.332</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R6" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="V6" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X6" t="n">
         <v>6</v>
@@ -1455,16 +1522,16 @@
         <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>103.1</v>
+        <v>102.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="AD6" t="n">
         <v>18</v>
@@ -1482,46 +1549,46 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1533,13 +1600,13 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.577</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
@@ -1589,34 +1656,34 @@
         <v>37.8</v>
       </c>
       <c r="J7" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
         <v>0.45</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M7" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>0.339</v>
       </c>
       <c r="O7" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="R7" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="S7" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="T7" t="n">
         <v>45.6</v>
@@ -1628,37 +1695,37 @@
         <v>13.6</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X7" t="n">
         <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
         <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
         <v>4</v>
@@ -1673,55 +1740,55 @@
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
         <v>7</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1831,22 +1898,22 @@
         <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -1864,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
@@ -1873,13 +1940,13 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
         <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1894,7 +1961,7 @@
         <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ8" t="n">
         <v>23</v>
@@ -1903,7 +1970,7 @@
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -1935,49 +2002,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J9" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K9" t="n">
         <v>0.461</v>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M9" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R9" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S9" t="n">
         <v>29.5</v>
@@ -1989,40 +2056,40 @@
         <v>21.4</v>
       </c>
       <c r="V9" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>95.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>10</v>
@@ -2034,28 +2101,28 @@
         <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
         <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AS9" t="n">
         <v>21</v>
@@ -2064,31 +2131,31 @@
         <v>25</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
         <v>5</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,19 +2283,19 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>19</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
         <v>26</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
@@ -2240,13 +2307,13 @@
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2261,7 +2328,7 @@
         <v>28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2389,13 +2456,13 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
         <v>24</v>
@@ -2413,22 +2480,22 @@
         <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
@@ -2443,10 +2510,10 @@
         <v>27</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2580,19 +2647,19 @@
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM12" t="n">
         <v>10</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP12" t="n">
         <v>28</v>
@@ -2604,25 +2671,25 @@
         <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>27</v>
@@ -2631,10 +2698,10 @@
         <v>13</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2756,10 +2823,10 @@
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2777,7 +2844,7 @@
         <v>29</v>
       </c>
       <c r="AP13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ13" t="n">
         <v>28</v>
@@ -2786,10 +2853,10 @@
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
         <v>19</v>
@@ -2810,7 +2877,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.471</v>
@@ -2872,31 +2939,31 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="P14" t="n">
-        <v>27.9</v>
+        <v>27.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="T14" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V14" t="n">
         <v>14.3</v>
@@ -2905,28 +2972,28 @@
         <v>9.4</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.8</v>
+        <v>107.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
@@ -2941,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK14" t="n">
         <v>5</v>
@@ -2950,10 +3017,10 @@
         <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2962,16 +3029,16 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,16 +3050,16 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA14" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3193,7 @@
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>26</v>
@@ -3138,19 +3205,19 @@
         <v>23</v>
       </c>
       <c r="AO15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP15" t="n">
         <v>13</v>
       </c>
-      <c r="AP15" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
         <v>30</v>
@@ -3168,7 +3235,7 @@
         <v>23</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3357,7 @@
         <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
         <v>14</v>
@@ -3302,22 +3369,22 @@
         <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
         <v>10</v>
       </c>
       <c r="AM16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -3332,7 +3399,7 @@
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
         <v>24</v>
@@ -3341,7 +3408,7 @@
         <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
@@ -3356,13 +3423,13 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.464</v>
+        <v>0.448</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,43 +3476,43 @@
         <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>82.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M17" t="n">
         <v>14.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R17" t="n">
         <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="T17" t="n">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
       <c r="U17" t="n">
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W17" t="n">
         <v>6.9</v>
@@ -3457,40 +3524,40 @@
         <v>5.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG17" t="n">
         <v>18</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI17" t="n">
         <v>17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
         <v>25</v>
@@ -3499,7 +3566,7 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
@@ -3514,25 +3581,25 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
         <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
         <v>21</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3544,7 +3611,7 @@
         <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3730,7 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI18" t="n">
         <v>23</v>
@@ -3720,7 +3787,7 @@
         <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3921,7 @@
         <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
@@ -3875,7 +3942,7 @@
         <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
         <v>20</v>
@@ -3896,7 +3963,7 @@
         <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4085,7 @@
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4048,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>23</v>
@@ -4081,16 +4148,16 @@
         <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
         <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4119,100 +4186,100 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.407</v>
+        <v>0.423</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J21" t="n">
-        <v>86.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="M21" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P21" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="T21" t="n">
-        <v>42.6</v>
+        <v>43.3</v>
       </c>
       <c r="U21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V21" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ21" t="n">
         <v>2</v>
@@ -4239,13 +4306,13 @@
         <v>4</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT21" t="n">
         <v>7</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9</v>
       </c>
       <c r="AU21" t="n">
         <v>4</v>
@@ -4260,10 +4327,10 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>0.107</v>
+        <v>0.111</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
@@ -4319,67 +4386,67 @@
         <v>35.6</v>
       </c>
       <c r="J22" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.435</v>
       </c>
       <c r="L22" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M22" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="O22" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q22" t="n">
         <v>0.747</v>
       </c>
       <c r="R22" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T22" t="n">
         <v>41.6</v>
       </c>
       <c r="U22" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V22" t="n">
         <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC22" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4409,16 +4476,16 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
@@ -4436,19 +4503,19 @@
         <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>5.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>18</v>
@@ -4755,7 +4822,7 @@
         <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>21</v>
@@ -4764,7 +4831,7 @@
         <v>10</v>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4779,10 +4846,10 @@
         <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
         <v>14</v>
@@ -4809,10 +4876,10 @@
         <v>19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
         <v>28</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
         <v>11</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>5</v>
@@ -4964,7 +5031,7 @@
         <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
@@ -4976,10 +5043,10 @@
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -5000,7 +5067,7 @@
         <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5029,58 +5096,58 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.781</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
         <v>13.6</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
@@ -5089,46 +5156,46 @@
         <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="n">
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ26" t="n">
         <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5140,13 +5207,13 @@
         <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>2</v>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU26" t="n">
         <v>11</v>
@@ -5173,16 +5240,16 @@
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB26" t="n">
         <v>14</v>
       </c>
-      <c r="BA26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>11</v>
-      </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG27" t="n">
         <v>27</v>
@@ -5304,7 +5371,7 @@
         <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -5322,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="AO27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
         <v>24</v>
@@ -5331,7 +5398,7 @@
         <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>23</v>
@@ -5358,7 +5425,7 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5474,25 +5541,25 @@
         <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ28" t="n">
         <v>19</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>3</v>
@@ -5510,22 +5577,22 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5534,7 +5601,7 @@
         <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>29</v>
       </c>
       <c r="BB28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5668,7 +5735,7 @@
         <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ29" t="n">
         <v>20</v>
@@ -5683,10 +5750,10 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
         <v>25</v>
@@ -5698,13 +5765,13 @@
         <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>6</v>
@@ -5716,13 +5783,13 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5974,7 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
@@ -5939,91 +6006,91 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.16</v>
+        <v>0.167</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.5</v>
       </c>
       <c r="J31" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M31" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.322</v>
+        <v>0.319</v>
       </c>
       <c r="O31" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="R31" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S31" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T31" t="n">
         <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V31" t="n">
         <v>13.8</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y31" t="n">
         <v>4.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6032,13 +6099,13 @@
         <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL31" t="n">
         <v>20</v>
@@ -6050,46 +6117,46 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>14</v>
       </c>
       <c r="AS31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU31" t="n">
         <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-21-2008-09</t>
+          <t>2008-12-21</t>
         </is>
       </c>
     </row>
